--- a/backend/data/corbett-hotel-sheet.xlsx
+++ b/backend/data/corbett-hotel-sheet.xlsx
@@ -2818,7 +2818,7 @@
         <v>Green Retreat Resort</v>
       </c>
       <c r="B62" t="str">
-        <v>Madanpur Chhoi</v>
+        <v>Chhoi</v>
       </c>
       <c r="C62">
         <v>43</v>
@@ -4171,7 +4171,7 @@
         <v>Trinantara Resort &amp; Spa</v>
       </c>
       <c r="B98" t="str">
-        <v>Khempur Chhoi</v>
+        <v>Chhoi</v>
       </c>
       <c r="C98">
         <v>100</v>

--- a/backend/data/corbett-hotel-sheet.xlsx
+++ b/backend/data/corbett-hotel-sheet.xlsx
@@ -2151,9 +2151,6 @@
       <c r="K47" t="str">
         <v>9015242000</v>
       </c>
-      <c r="L47" t="str">
-        <v>Message shared no response</v>
-      </c>
       <c r="P47" t="str">
         <v>17</v>
       </c>
@@ -2533,9 +2530,6 @@
       <c r="H55" t="str">
         <v>info@clarissaresorts.com</v>
       </c>
-      <c r="L55" t="str">
-        <v>Message shared no response</v>
-      </c>
       <c r="S55" t="str">
         <v>Kashish</v>
       </c>
@@ -2715,9 +2709,6 @@
       <c r="H59" t="str">
         <v>sales@harmonyhotels.co.in</v>
       </c>
-      <c r="L59" t="str">
-        <v>Not Answering</v>
-      </c>
       <c r="P59" t="str">
         <v>120</v>
       </c>
@@ -2841,9 +2832,6 @@
       <c r="I62" t="str">
         <v>Anil</v>
       </c>
-      <c r="L62" t="str">
-        <v>Message shared no response</v>
-      </c>
       <c r="S62" t="str">
         <v>Kashish</v>
       </c>
@@ -2879,9 +2867,6 @@
       <c r="K63" t="str">
         <v>9520990494</v>
       </c>
-      <c r="L63" t="str">
-        <v>Message shared no response</v>
-      </c>
       <c r="P63" t="str">
         <v>144</v>
       </c>
@@ -2917,9 +2902,6 @@
       <c r="H64" t="str">
         <v>creekwoodresortkyari@gmail.com</v>
       </c>
-      <c r="L64" t="str">
-        <v>Message shared no response</v>
-      </c>
       <c r="S64" t="str">
         <v>Kashish</v>
       </c>
@@ -2996,9 +2978,6 @@
       <c r="H66" t="str">
         <v>crs@sterlingholidays.com</v>
       </c>
-      <c r="L66" t="str">
-        <v>Not Answering</v>
-      </c>
       <c r="S66" t="str">
         <v>Kashish</v>
       </c>
@@ -3019,9 +2998,6 @@
       <c r="H67" t="str">
         <v>sales@leroihotels.com</v>
       </c>
-      <c r="L67" t="str">
-        <v>Not Answering</v>
-      </c>
       <c r="S67" t="str">
         <v>Kashish</v>
       </c>
@@ -3253,9 +3229,6 @@
       <c r="D73" t="str">
         <v>https://www.makemytrip.com/hotels/address-of-bentocorbettwoodsresort-details_-jimcor_bettram_nagar._html_</v>
       </c>
-      <c r="L73" t="str">
-        <v>Not able to connect</v>
-      </c>
       <c r="S73" t="str">
         <v>Kashish</v>
       </c>
@@ -3352,9 +3325,6 @@
       <c r="H76" t="str">
         <v>reservations@aahmahospitality.com</v>
       </c>
-      <c r="N76" t="str">
-        <v>outside vendor not allowed</v>
-      </c>
       <c r="P76" t="str">
         <v>250-300</v>
       </c>
@@ -3378,9 +3348,6 @@
       <c r="H77" t="str">
         <v>sales@treffresort.com</v>
       </c>
-      <c r="L77" t="str">
-        <v>Will arrange a call back</v>
-      </c>
       <c r="S77" t="str">
         <v>Kashish</v>
       </c>
@@ -3424,9 +3391,6 @@
       <c r="H79" t="str">
         <v>info@tuskarsresort.com</v>
       </c>
-      <c r="L79" t="str">
-        <v>Will arrange a call back</v>
-      </c>
       <c r="P79" t="str">
         <v>60</v>
       </c>
@@ -3651,9 +3615,6 @@
       </c>
       <c r="H85" t="str">
         <v>info@sshubhhotels.com</v>
-      </c>
-      <c r="I85" t="str">
-        <v>Not able to connect</v>
       </c>
       <c r="S85" t="str">
         <v>Kashish</v>
